--- a/LISTAS/ma/MANIJA FIJA.xlsx
+++ b/LISTAS/ma/MANIJA FIJA.xlsx
@@ -802,14 +802,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45163.60889146272</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -855,27 +851,6 @@
       </c>
       <c r="E11" s="13" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="18" customHeight="1" s="1">
       <c r="A33" s="22" t="inlineStr">
         <is>
@@ -908,7 +883,7 @@
       </c>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="31" t="n">
-        <v>87.289</v>
+        <v>100.382</v>
       </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="32" t="n"/>
@@ -926,7 +901,7 @@
       </c>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="33" t="n">
-        <v>123.677</v>
+        <v>142.229</v>
       </c>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="32" t="n"/>
@@ -944,7 +919,7 @@
       </c>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="31" t="n">
-        <v>167.319</v>
+        <v>192.417</v>
       </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="32" t="n"/>
@@ -962,14 +937,13 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="31" t="n">
-        <v>275.661</v>
+        <v>317.01</v>
       </c>
       <c r="E37" s="4" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="1">
       <c r="E38" s="4" t="n"/>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -977,9 +951,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
@@ -987,29 +958,20 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
     <row r="54" ht="18" customHeight="1" s="1">
       <c r="A54" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/MANIJA FIJA.xlsx
+++ b/LISTAS/ma/MANIJA FIJA.xlsx
@@ -802,7 +802,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45237</v>
+        <v>45244</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
@@ -963,15 +963,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/MANIJA FIJA.xlsx
+++ b/LISTAS/ma/MANIJA FIJA.xlsx
@@ -802,7 +802,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/MANIJA FIJA.xlsx
+++ b/LISTAS/ma/MANIJA FIJA.xlsx
@@ -802,7 +802,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
@@ -963,15 +963,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/MANIJA FIJA.xlsx
+++ b/LISTAS/ma/MANIJA FIJA.xlsx
@@ -802,7 +802,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/MANIJA FIJA.xlsx
+++ b/LISTAS/ma/MANIJA FIJA.xlsx
@@ -802,10 +802,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45266</v>
+        <v>45261.57773398303</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -851,6 +855,27 @@
       </c>
       <c r="E11" s="13" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33" ht="18" customHeight="1" s="1">
       <c r="A33" s="22" t="inlineStr">
         <is>
@@ -883,7 +908,7 @@
       </c>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="31" t="n">
-        <v>100.382</v>
+        <v>160.72</v>
       </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="32" t="n"/>
@@ -901,7 +926,7 @@
       </c>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="33" t="n">
-        <v>142.229</v>
+        <v>227.72</v>
       </c>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="32" t="n"/>
@@ -919,7 +944,7 @@
       </c>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="31" t="n">
-        <v>192.417</v>
+        <v>308.1</v>
       </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="32" t="n"/>
@@ -937,13 +962,14 @@
       </c>
       <c r="C37" s="29" t="n"/>
       <c r="D37" s="31" t="n">
-        <v>317.01</v>
+        <v>508</v>
       </c>
       <c r="E37" s="4" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1" s="1">
       <c r="E38" s="4" t="n"/>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -951,6 +977,9 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
@@ -958,20 +987,29 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
     <row r="54" ht="18" customHeight="1" s="1">
       <c r="A54" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/MANIJA FIJA.xlsx
+++ b/LISTAS/ma/MANIJA FIJA.xlsx
@@ -802,14 +802,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="n">
-        <v>45261.57773398303</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -855,27 +851,6 @@
       </c>
       <c r="E11" s="13" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="18" customHeight="1" s="1">
       <c r="A33" s="22" t="inlineStr">
         <is>
@@ -908,7 +883,7 @@
       </c>
       <c r="C34" s="29" t="n"/>
       <c r="D34" s="31" t="n">
-        <v>160.72</v>
+        <v>100.382</v>
       </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="32" t="n"/>
@@ -926,7 +901,7 @@
       </c>
       <c r="C35" s="29" t="n"/>
       <c r="D35" s="33" t="n">
-        <v>227.72</v>
+        <v>142.229</v>
       </c>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="32" t="n"/>
@@ -944,7 +919,7 @@
       </c>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="31" t="n">
-        <v>308.1</v>
+        <v>192.417</v>
       </c>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="32" t="n"/>
@@ -969,7 +944,6 @@
     <row r="38" ht="18" customHeight="1" s="1">
       <c r="E38" s="4" t="n"/>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -977,9 +951,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
@@ -987,29 +958,20 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
     <row r="54" ht="18" customHeight="1" s="1">
       <c r="A54" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
